--- a/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,95; 77,46</t>
+          <t>52,68; 77,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,14; 79,21</t>
+          <t>58,9; 78,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,41; 75,36</t>
+          <t>58,4; 74,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>60,02; 77,42</t>
+          <t>59,81; 77,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,22; 81,17</t>
+          <t>69,01; 81,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,99; 77,35</t>
+          <t>66,18; 77,49</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,3; 76,53</t>
+          <t>65,55; 76,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,66; 75,93</t>
+          <t>67,0; 76,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,16; 74,5</t>
+          <t>67,15; 74,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,21; 79,11</t>
+          <t>69,43; 79,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,31; 77,77</t>
+          <t>48,56; 77,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,46; 76,6</t>
+          <t>59,6; 76,59</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,79; 83,01</t>
+          <t>73,96; 82,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,58; 79,25</t>
+          <t>71,76; 79,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,0; 79,53</t>
+          <t>74,04; 79,68</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,29; 81,17</t>
+          <t>71,56; 81,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,32; 97,32</t>
+          <t>80,45; 97,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,12; 95,71</t>
+          <t>78,2; 94,9</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,64; 82,89</t>
+          <t>72,37; 83,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,49; 88,67</t>
+          <t>82,73; 88,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,62; 85,46</t>
+          <t>80,0; 85,56</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,89; 76,0</t>
+          <t>70,85; 75,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,6; 84,43</t>
+          <t>73,65; 84,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,19</t>
+          <t>73,41; 80,12</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99217; 145143</t>
+          <t>98703; 145082</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93033; 124597</t>
+          <t>92649; 123267</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204758; 259752</t>
+          <t>201298; 257853</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112131; 144644</t>
+          <t>111747; 144042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>133092; 160705</t>
+          <t>136647; 160752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>257783; 297660</t>
+          <t>254655; 298205</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>192886; 226046</t>
+          <t>193609; 224916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>171570; 195416</t>
+          <t>172434; 195702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>371220; 411777</t>
+          <t>371161; 412270</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>231043; 264085</t>
+          <t>231789; 263864</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173605; 279457</t>
+          <t>174498; 277998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>412158; 530970</t>
+          <t>413132; 530923</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>226606; 254916</t>
+          <t>227143; 253883</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>210574; 233130</t>
+          <t>211105; 232498</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>444961; 478181</t>
+          <t>445183; 479066</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>138683; 157889</t>
+          <t>139201; 158055</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>325484; 394333</t>
+          <t>326013; 394750</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>468488; 573994</t>
+          <t>468985; 569161</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>108969; 124347</t>
+          <t>108570; 125108</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>195017; 209616</t>
+          <t>195584; 209893</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307690; 330240</t>
+          <t>309123; 330621</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1173195; 1257849</t>
+          <t>1172583; 1257039</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1404113; 1610666</t>
+          <t>1405072; 1605310</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2613514; 2857112</t>
+          <t>2615583; 2854479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,68; 77,43</t>
+          <t>57,85; 79,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,9; 78,37</t>
+          <t>61,61; 79,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,4; 74,81</t>
+          <t>62,48; 77,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,81; 77,1</t>
+          <t>59,62; 75,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,01; 81,19</t>
+          <t>69,96; 81,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,18; 77,49</t>
+          <t>66,72; 77,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,55; 76,15</t>
+          <t>66,35; 76,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,0; 76,04</t>
+          <t>66,76; 75,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,15; 74,59</t>
+          <t>68,03; 75,22</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,43; 79,04</t>
+          <t>69,17; 78,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,56; 77,36</t>
+          <t>72,79; 79,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,6; 76,59</t>
+          <t>72,06; 78,05</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 82,67</t>
+          <t>73,96; 83,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 79,04</t>
+          <t>70,92; 78,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,04; 79,68</t>
+          <t>73,97; 80,02</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,56; 81,25</t>
+          <t>71,33; 81,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,45; 97,42</t>
+          <t>77,85; 84,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,2; 94,9</t>
+          <t>75,79; 82,04</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,37; 83,39</t>
+          <t>71,81; 82,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,73; 88,79</t>
+          <t>82,31; 88,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,0; 85,56</t>
+          <t>79,56; 85,29</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,85; 75,95</t>
+          <t>71,31; 76,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,65; 84,14</t>
+          <t>74,97; 78,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73,41; 80,12</t>
+          <t>73,95; 76,8</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>123927</t>
+          <t>127919</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>108808</t>
+          <t>128341</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232735</t>
+          <t>256260</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98703; 145082</t>
+          <t>106452; 145832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92649; 123267</t>
+          <t>111641; 143401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201298; 257853</t>
+          <t>228199; 282420</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>128936</t>
+          <t>147057</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>171194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278226</t>
+          <t>318251</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>111747; 144042</t>
+          <t>128867; 164028</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>136647; 160752</t>
+          <t>156580; 183115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254655; 298205</t>
+          <t>293545; 339201</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>209841</t>
+          <t>242534</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>183849</t>
+          <t>210114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>393690</t>
+          <t>452647</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>193609; 224916</t>
+          <t>224191; 258555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172434; 195702</t>
+          <t>196212; 222907</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>371161; 412270</t>
+          <t>429777; 475251</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>259991</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>249509</t>
+          <t>270421</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497808</t>
+          <t>530412</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>231789; 263864</t>
+          <t>242987; 275398</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>174498; 277998</t>
+          <t>257687; 282814</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>413132; 530923</t>
+          <t>508268; 550461</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>262206</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>245729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463162</t>
+          <t>507935</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>227143; 253883</t>
+          <t>246421; 277550</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>211105; 232498</t>
+          <t>231364; 257449</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>445183; 479066</t>
+          <t>487757; 527702</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>148802</t>
+          <t>164478</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>368435</t>
+          <t>180238</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>344716</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>139201; 158055</t>
+          <t>153161; 174126</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>326013; 394750</t>
+          <t>172119; 187532</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>468985; 569161</t>
+          <t>330309; 357556</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>117115</t>
+          <t>127046</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202976</t>
+          <t>220127</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>320091</t>
+          <t>347173</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>108570; 125108</t>
+          <t>117643; 134932</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>195584; 209893</t>
+          <t>210896; 227399</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>309123; 330621</t>
+          <t>334173; 358251</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1172583; 1257039</t>
+          <t>1284265; 1369981</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1405072; 1605310</t>
+          <t>1391742; 1458383</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2615583; 2854479</t>
+          <t>2704879; 2809037</t>
         </is>
       </c>
     </row>
